--- a/test/fixtures/bulk_single_relations_test.xlsx
+++ b/test/fixtures/bulk_single_relations_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bluetab/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzo.sanchez/workspace/truedat/back/td-lm/test/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBC05371-8E17-774F-A323-F9AF3D4E0A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED53979-91A2-154E-A32E-9B8C32A282CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5240" yWindow="500" windowWidth="27100" windowHeight="13380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="24000" windowHeight="13380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>concept_name</t>
   </si>
@@ -44,6 +44,12 @@
   </si>
   <si>
     <t>xzy_tag</t>
+  </si>
+  <si>
+    <t>concept_type</t>
+  </si>
+  <si>
+    <t>foo_concept_type</t>
   </si>
 </sst>
 </file>
@@ -386,57 +392,63 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D300"/>
+  <dimension ref="A1:E300"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
